--- a/Dekauto.Export.Service/Templates/diploma_supplement/sbm/bachelor_2_page.xlsx
+++ b/Dekauto.Export.Service/Templates/diploma_supplement/sbm/bachelor_2_page.xlsx
@@ -1998,7 +1998,7 @@
       <c r="H10" s="3"/>
     </row>
   </sheetData>
-  <sheetProtection password="DBF4" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection objects="1" password="DBF4" scenarios="1" sheet="1"/>
   <mergeCells count="2">
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="C8:D8"/>
@@ -21496,7 +21496,7 @@
       <c r="DF171" s="29"/>
     </row>
   </sheetData>
-  <sheetProtection password="DBF4" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection objects="1" password="DBF4" scenarios="1" sheet="1"/>
   <mergeCells count="135">
     <mergeCell ref="CF22:CY25"/>
     <mergeCell ref="AO29:AX30"/>
@@ -27641,7 +27641,7 @@
       <c r="BC84" s="28"/>
     </row>
   </sheetData>
-  <sheetProtection password="DBF4" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection objects="1" password="DBF4" scenarios="1" sheet="1"/>
   <mergeCells count="402">
     <mergeCell ref="AE13:AP13"/>
     <mergeCell ref="AR13:AU13"/>
@@ -28310,7 +28310,7 @@
       <c r="F21" s="3"/>
     </row>
   </sheetData>
-  <sheetProtection password="DBF4" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection objects="1" password="DBF4" scenarios="1" sheet="1"/>
   <mergeCells count="5">
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="C1:E1"/>
@@ -30608,7 +30608,7 @@
       <c r="F135" s="3"/>
     </row>
   </sheetData>
-  <sheetProtection password="DBF4" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection objects="1" password="DBF4" scenarios="1" sheet="1"/>
   <conditionalFormatting sqref="E2:E134">
     <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
       <formula>75</formula>
@@ -31349,7 +31349,7 @@
       <c r="E14" s="94"/>
     </row>
   </sheetData>
-  <sheetProtection password="DBF4" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection objects="1" password="DBF4" scenarios="1" sheet="1"/>
   <conditionalFormatting sqref="D2">
     <cfRule type="cellIs" dxfId="3" priority="8" operator="greaterThan">
       <formula>118</formula>
@@ -50247,7 +50247,7 @@
       <c r="DF167" s="29"/>
     </row>
   </sheetData>
-  <sheetProtection password="DBF4" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection objects="1" password="DBF4" scenarios="1" sheet="1"/>
   <mergeCells count="47">
     <mergeCell ref="CF23:CZ27"/>
     <mergeCell ref="CF35:CZ40"/>
@@ -56192,7 +56192,7 @@
       <c r="BA84" s="28"/>
     </row>
   </sheetData>
-  <sheetProtection password="DBF4" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection objects="1" password="DBF4" scenarios="1" sheet="1"/>
   <mergeCells count="408">
     <mergeCell ref="AR81:AU81"/>
     <mergeCell ref="AV81:AZ81"/>
